--- a/resultados/Resultados_Roberta-Base-FT.xlsx
+++ b/resultados/Resultados_Roberta-Base-FT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UMA\TFG\TFG-Sistema-Recomendacion-Personalidad\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBF68BB-57CD-4FAA-A2B9-E25FD4FA4546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AFBFDF-4C58-4457-8D4E-E425F8503309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="289">
   <si>
     <t>Modelos</t>
   </si>
@@ -45,6 +45,1103 @@
   </si>
   <si>
     <t>Matriz Confusion</t>
+  </si>
+  <si>
+    <t>Parametros</t>
+  </si>
+  <si>
+    <t>{'penalty': None, 'C': 9.732719859279047, 'solver': 'lbfgs', 'tol': 0.00010564097578389837, 'class_weight': 'balanced', 'random_state': 42, 'n_jobs': -1, 'max_iter': 5000}</t>
+  </si>
+  <si>
+    <t>LR E/I</t>
+  </si>
+  <si>
+    <t>0: 0.41
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.67</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.77</t>
+  </si>
+  <si>
+    <t>0: 200
+1: 668</t>
+  </si>
+  <si>
+    <t>[[150 50]
+ [220 448]]</t>
+  </si>
+  <si>
+    <t>LR S/N</t>
+  </si>
+  <si>
+    <t>0: 0.33
+1: 0.95</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.76</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.84</t>
+  </si>
+  <si>
+    <t>0: 120
+1: 748</t>
+  </si>
+  <si>
+    <t>[[88 32]
+ [181 567]]</t>
+  </si>
+  <si>
+    <t>LR T/F</t>
+  </si>
+  <si>
+    <t>0: 0.77
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 0.78
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.78
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 398
+1: 470</t>
+  </si>
+  <si>
+    <t>[[312 86]
+ [95 375]]</t>
+  </si>
+  <si>
+    <t>LR J/P</t>
+  </si>
+  <si>
+    <t>0: 0.66
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.74</t>
+  </si>
+  <si>
+    <t>0: 0.70
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 344
+1: 524</t>
+  </si>
+  <si>
+    <t>[[257 87]
+ [134 390]]</t>
+  </si>
+  <si>
+    <t>{'n_estimators': 352, 'max_depth': 8, 'learning_rate': 0.041694500859353036, 'subsample': 0.6688508428769014, 'colsample_bytree': 0.6246885857257476, 'gamma': 0.6844100651211652, 'tree_method': 'hist', 'device': 'cuda', 'random_state': 42, 'n_jobs': 1}</t>
+  </si>
+  <si>
+    <t>XGB E/I</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.72
+1: 0.76</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.82</t>
+  </si>
+  <si>
+    <t>[[144 56]
+ [161 507]]</t>
+  </si>
+  <si>
+    <t>XGB S/N</t>
+  </si>
+  <si>
+    <t>0: 0.43
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.61
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.90</t>
+  </si>
+  <si>
+    <t>[[73 47]
+ [98 650]]</t>
+  </si>
+  <si>
+    <t>XGB T/F</t>
+  </si>
+  <si>
+    <t>0: 0.80
+1: 0.84</t>
+  </si>
+  <si>
+    <t>0: 0.81
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[324 74]
+ [82 388]]</t>
+  </si>
+  <si>
+    <t>XGB J/P</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 0.63
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.69
+1: 0.82</t>
+  </si>
+  <si>
+    <t>[[217 127]
+ [72 452]]</t>
+  </si>
+  <si>
+    <t>{'loss': 'squared_hinge', 'C': 9.605448156429867, 'tol': 0.0004119653918147926, 'fit_intercept': False, 'random_state': 42, 'class_weight': 'balanced', 'max_iter': 5000}</t>
+  </si>
+  <si>
+    <t>LSVC E/I</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.77
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[153 47]
+ [180 488]]</t>
+  </si>
+  <si>
+    <t>LSVC S/N</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.54
+1: 0.91</t>
+  </si>
+  <si>
+    <t>[[75 45]
+ [84 664]]</t>
+  </si>
+  <si>
+    <t>LSVC T/F</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.80
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 0.77
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[318 80]
+ [105 365]]</t>
+  </si>
+  <si>
+    <t>LSVC J/P</t>
+  </si>
+  <si>
+    <t>0: 0.69
+1: 0.79</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[234 110]
+ [107 417]]</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (256, 128, 64), 'activation': 'tanh', 'solver': 'adam', 'learning_rate': 'constant', 'learning_rate_init': 0.001, 'early_stopping': True, 'max_iter': 6000, 'random_state': 42}</t>
+  </si>
+  <si>
+    <t>MLPC E/I</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.75</t>
+  </si>
+  <si>
+    <t>[[147 53]
+ [167 501]]</t>
+  </si>
+  <si>
+    <t>MLPC S/N</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.90</t>
+  </si>
+  <si>
+    <t>[[82 38]
+ [111 637]]</t>
+  </si>
+  <si>
+    <t>MLPC T/F</t>
+  </si>
+  <si>
+    <t>0: 0.79
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.79
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[314 84]
+ [82 388]]</t>
+  </si>
+  <si>
+    <t>MLPC J/P</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.70
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[212 132]
+ [52 472]]</t>
+  </si>
+  <si>
+    <t>{'n_neighbors': 2, 'weights': 'distance', 'algorithm': 'brute', 'leaf_size': 14, 'metric': 'cosine', 'n_jobs': -1}</t>
+  </si>
+  <si>
+    <t>KNC E/I</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[135 65]
+ [188 480]]</t>
+  </si>
+  <si>
+    <t>KNC S/N</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 0.43
+1: 0.87</t>
+  </si>
+  <si>
+    <t>[[72 48]
+ [141 607]]</t>
+  </si>
+  <si>
+    <t>KNC T/F</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[290 108]
+ [108 362]]</t>
+  </si>
+  <si>
+    <t>KNC J/P</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.70</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.71</t>
+  </si>
+  <si>
+    <t>0: 0.54
+1: 0.71</t>
+  </si>
+  <si>
+    <t>[[184 160]
+ [150 374]]</t>
+  </si>
+  <si>
+    <t>{'criterion': 'gini', 'max_depth': 15, 'min_samples_split': 9, 'min_samples_leaf': 4, 'max_features': None, 'class_weight': None, 'random_state': 42}</t>
+  </si>
+  <si>
+    <t>DTC E/I</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.70
+1: 0.71</t>
+  </si>
+  <si>
+    <t>[[140 60]
+ [194 474]]</t>
+  </si>
+  <si>
+    <t>DTC S/N</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.67
+1: 0.83</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.88</t>
+  </si>
+  <si>
+    <t>[[80 40]
+ [126 622]]</t>
+  </si>
+  <si>
+    <t>DTC T/F</t>
+  </si>
+  <si>
+    <t>0: 0.72
+1: 0.79</t>
+  </si>
+  <si>
+    <t>0: 0.77
+1: 0.74</t>
+  </si>
+  <si>
+    <t>0: 0.74
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[307 91]
+ [121 349]]</t>
+  </si>
+  <si>
+    <t>DTC J/P</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.59
+1: 0.69</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.71</t>
+  </si>
+  <si>
+    <t>[[202 142]
+ [161 363]]</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.66
+1: 0.75</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[132 68]
+ [164 504]]</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.61
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.87</t>
+  </si>
+  <si>
+    <t>[[73 47]
+ [132 616]]</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.87</t>
+  </si>
+  <si>
+    <t>[[115 85]
+ [88 580]]</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[58 62]
+ [63 685]]</t>
+  </si>
+  <si>
+    <t>0: 0.74
+1: 0.73</t>
+  </si>
+  <si>
+    <t>[[149 51]
+ [178 490]]</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.89</t>
+  </si>
+  <si>
+    <t>[[72 48]
+ [108 640]]</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.64
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.87</t>
+  </si>
+  <si>
+    <t>[[128 72]
+ [101 567]]</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.90</t>
+  </si>
+  <si>
+    <t>[[59 61]
+ [92 656]]</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.72
+1: 0.61</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.72</t>
+  </si>
+  <si>
+    <t>[[144 56]
+ [258 410]]</t>
+  </si>
+  <si>
+    <t>0: 0.24
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.66</t>
+  </si>
+  <si>
+    <t>0: 0.35
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[81 39]
+ [257 491]]</t>
+  </si>
+  <si>
+    <t>0: 0.41
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.63
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[126 74]
+ [182 486]]</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.59
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[71 49]
+ [165 583]]</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.69
+1: 0.75</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.82</t>
+  </si>
+  <si>
+    <t>[[139 61]
+ [165 503]]</t>
+  </si>
+  <si>
+    <t>0: 0.59
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[71 49]
+ [126 622]]</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.87</t>
+  </si>
+  <si>
+    <t>[[116 84]
+ [90 578]]</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.51
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[64 56]
+ [69 679]]</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.74
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[149 51]
+ [184 484]]</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.93</t>
+  </si>
+  <si>
+    <t>[[54 66]
+ [47 701]]</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.76
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[151 49]
+ [184 484]]</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[62 58]
+ [67 681]]</t>
+  </si>
+  <si>
+    <t>[[145 55]
+ [263 405]]</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.63
+1: 0.71</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[76 44]
+ [220 528]]</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.75</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[120 80]
+ [164 504]]</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.85</t>
+  </si>
+  <si>
+    <t>[[64 56]
+ [150 598]]</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.70
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.54
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[140 60]
+ [179 489]]</t>
+  </si>
+  <si>
+    <t>0: 0.63
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.86</t>
+  </si>
+  <si>
+    <t>[[76 44]
+ [149 599]]</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.61
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.86</t>
+  </si>
+  <si>
+    <t>[[122 78]
+ [101 567]]</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.91</t>
+  </si>
+  <si>
+    <t>[[64 56]
+ [70 678]]</t>
+  </si>
+  <si>
+    <t>0: 0.72
+1: 0.74</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[144 56]
+ [175 493]]</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[54 66]
+ [60 688]]</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.86</t>
+  </si>
+  <si>
+    <t>[[113 87]
+ [99 569]]</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[47 73]
+ [55 693]]</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.58</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.70</t>
+  </si>
+  <si>
+    <t>[[146 54]
+ [280 388]]</t>
+  </si>
+  <si>
+    <t>0: 0.22
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.62</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.74</t>
+  </si>
+  <si>
+    <t>[[82 38]
+ [284 464]]</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.70</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[124 76]
+ [201 467]]</t>
+  </si>
+  <si>
+    <t>0: 0.29
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.75</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[75 45]
+ [188 560]]</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.70</t>
+  </si>
+  <si>
+    <t>0: 0.54
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[146 54]
+ [199 469]]</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.95</t>
+  </si>
+  <si>
+    <t>0: 0.72
+1: 0.77</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.85</t>
+  </si>
+  <si>
+    <t>[[87 33]
+ [170 578]]</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[136 64]
+ [134 534]]</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.90</t>
+  </si>
+  <si>
+    <t>[[69 51]
+ [77 671]]</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.89</t>
+  </si>
+  <si>
+    <t>[[81 39]
+ [113 635]]</t>
+  </si>
+  <si>
+    <t>0: 0.66
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[132 68]
+ [134 534]]</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[69 51]
+ [69 679]]</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.65
+1: 0.75</t>
+  </si>
+  <si>
+    <t>[[130 70]
+ [165 503]]</t>
+  </si>
+  <si>
+    <t>0: 0.33
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.82</t>
+  </si>
+  <si>
+    <t>[[64 56]
+ [131 617]]</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.65
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.51
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[130 70]
+ [179 489]]</t>
+  </si>
+  <si>
+    <t>0: 0.51
+1: 0.90</t>
+  </si>
+  <si>
+    <t>[[76 44]
+ [104 644]]</t>
   </si>
 </sst>
 </file>
@@ -72,12 +1169,48 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -122,13 +1255,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,13 +1607,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:G3"/>
+  <dimension ref="A3:K32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="10" max="10" width="30.140625" customWidth="1"/>
+    <col min="11" max="11" width="53.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -460,6 +1638,743 @@
       <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.86</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0.74</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.82</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0.79</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0.64</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+    </row>
+    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0.66</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0.64</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="6"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+    </row>
+    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0.71</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+    </row>
+    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+    </row>
+    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -468,10 +2383,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A3:G3"/>
+  <dimension ref="A3:K32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="53.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -493,6 +2414,743 @@
       <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.74</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.86</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0.73</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.87</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0.79</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0.73</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0.86</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0.63</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+    </row>
+    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0.7</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0.64</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="6"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+    </row>
+    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0.72</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+    </row>
+    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+    </row>
+    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -501,10 +3159,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:G2"/>
+  <dimension ref="A2:K31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" customWidth="1"/>
+    <col min="11" max="11" width="32.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -526,6 +3189,743 @@
       <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0.79</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0.73</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0.85</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.79</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0.62</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+    </row>
+    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0.63</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+    </row>
+    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0.64</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+    </row>
+    <row r="29" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0.73</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+    </row>
+    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -534,10 +3934,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A2:G2"/>
+  <dimension ref="A2:K31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" customWidth="1"/>
+    <col min="11" max="11" width="36.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -559,6 +3965,743 @@
       <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.71</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0.73</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0.82</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.79</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0.77</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0.86</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0.73</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+    </row>
+    <row r="24" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0.78</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+    </row>
+    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0.64</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0.71</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+    </row>
+    <row r="29" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+    </row>
+    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -567,10 +4710,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A2:G2"/>
+  <dimension ref="A2:K31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="58.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -592,6 +4741,743 @@
       <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.69</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.83</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0.74</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0.85</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.79</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0.71</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0.78</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+    </row>
+    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0.64</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0.71</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+    </row>
+    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+    </row>
+    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resultados/Resultados_Roberta-Base-FT.xlsx
+++ b/resultados/Resultados_Roberta-Base-FT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UMA\TFG\TFG-Sistema-Recomendacion-Personalidad\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AFBFDF-4C58-4457-8D4E-E425F8503309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FABBA1-5BC6-41BE-8A1C-2D1233154623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,13 +47,945 @@
     <t>Matriz Confusion</t>
   </si>
   <si>
+    <t>LR E/I</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.66
+1: 0.75</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 200
+1: 668</t>
+  </si>
+  <si>
+    <t>[[132 68]
+ [164 504]]</t>
+  </si>
+  <si>
+    <t>LR S/N</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.61
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 120
+1: 748</t>
+  </si>
+  <si>
+    <t>[[73 47]
+ [132 616]]</t>
+  </si>
+  <si>
     <t>Parametros</t>
   </si>
   <si>
     <t>{'penalty': None, 'C': 9.732719859279047, 'solver': 'lbfgs', 'tol': 0.00010564097578389837, 'class_weight': 'balanced', 'random_state': 42, 'n_jobs': -1, 'max_iter': 5000}</t>
   </si>
   <si>
-    <t>LR E/I</t>
+    <t>LR T/F</t>
+  </si>
+  <si>
+    <t>0: 0.77
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 0.78
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.78
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 398
+1: 470</t>
+  </si>
+  <si>
+    <t>[[312 86]
+ [95 375]]</t>
+  </si>
+  <si>
+    <t>LR J/P</t>
+  </si>
+  <si>
+    <t>0: 0.66
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.74</t>
+  </si>
+  <si>
+    <t>0: 0.70
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 344
+1: 524</t>
+  </si>
+  <si>
+    <t>[[257 87]
+ [134 390]]</t>
+  </si>
+  <si>
+    <t>XGB E/I</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.87</t>
+  </si>
+  <si>
+    <t>[[115 85]
+ [88 580]]</t>
+  </si>
+  <si>
+    <t>XGB S/N</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[58 62]
+ [63 685]]</t>
+  </si>
+  <si>
+    <t>{'n_estimators': 352, 'max_depth': 8, 'learning_rate': 0.041694500859353036, 'subsample': 0.6688508428769014, 'colsample_bytree': 0.6246885857257476, 'gamma': 0.6844100651211652, 'tree_method': 'hist', 'device': 'cuda', 'random_state': 42, 'n_jobs': 1}</t>
+  </si>
+  <si>
+    <t>XGB T/F</t>
+  </si>
+  <si>
+    <t>0: 0.80
+1: 0.84</t>
+  </si>
+  <si>
+    <t>0: 0.81
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[324 74]
+ [82 388]]</t>
+  </si>
+  <si>
+    <t>XGB J/P</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 0.63
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.69
+1: 0.82</t>
+  </si>
+  <si>
+    <t>[[217 127]
+ [72 452]]</t>
+  </si>
+  <si>
+    <t>LSVC E/I</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.74
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[149 51]
+ [178 490]]</t>
+  </si>
+  <si>
+    <t>LSVC S/N</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.89</t>
+  </si>
+  <si>
+    <t>[[72 48]
+ [108 640]]</t>
+  </si>
+  <si>
+    <t>{'loss': 'squared_hinge', 'C': 9.605448156429867, 'tol': 0.0004119653918147926, 'fit_intercept': False, 'random_state': 42, 'class_weight': 'balanced', 'max_iter': 5000}</t>
+  </si>
+  <si>
+    <t>LSVC T/F</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.80
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 0.77
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[318 80]
+ [105 365]]</t>
+  </si>
+  <si>
+    <t>LSVC J/P</t>
+  </si>
+  <si>
+    <t>0: 0.69
+1: 0.79</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[234 110]
+ [107 417]]</t>
+  </si>
+  <si>
+    <t>MLPC E/I</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.64
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.87</t>
+  </si>
+  <si>
+    <t>[[128 72]
+ [101 567]]</t>
+  </si>
+  <si>
+    <t>MLPC S/N</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.90</t>
+  </si>
+  <si>
+    <t>[[59 61]
+ [92 656]]</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (256, 128, 64), 'activation': 'tanh', 'solver': 'adam', 'learning_rate': 'constant', 'learning_rate_init': 0.001, 'early_stopping': True, 'max_iter': 6000, 'random_state': 42}</t>
+  </si>
+  <si>
+    <t>MLPC T/F</t>
+  </si>
+  <si>
+    <t>0: 0.79
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.79
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[314 84]
+ [82 388]]</t>
+  </si>
+  <si>
+    <t>MLPC J/P</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.70
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[212 132]
+ [52 472]]</t>
+  </si>
+  <si>
+    <t>KNC E/I</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.72
+1: 0.61</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.72</t>
+  </si>
+  <si>
+    <t>[[144 56]
+ [258 410]]</t>
+  </si>
+  <si>
+    <t>KNC S/N</t>
+  </si>
+  <si>
+    <t>0: 0.24
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.66</t>
+  </si>
+  <si>
+    <t>0: 0.35
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[81 39]
+ [257 491]]</t>
+  </si>
+  <si>
+    <t>{'n_neighbors': 2, 'weights': 'distance', 'algorithm': 'brute', 'leaf_size': 14, 'metric': 'cosine', 'n_jobs': -1}</t>
+  </si>
+  <si>
+    <t>KNC T/F</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[290 108]
+ [108 362]]</t>
+  </si>
+  <si>
+    <t>KNC J/P</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.70</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.71</t>
+  </si>
+  <si>
+    <t>0: 0.54
+1: 0.71</t>
+  </si>
+  <si>
+    <t>[[184 160]
+ [150 374]]</t>
+  </si>
+  <si>
+    <t>DTC E/I</t>
+  </si>
+  <si>
+    <t>0: 0.41
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.63
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[126 74]
+ [182 486]]</t>
+  </si>
+  <si>
+    <t>DTC S/N</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.59
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[71 49]
+ [165 583]]</t>
+  </si>
+  <si>
+    <t>{'criterion': 'gini', 'max_depth': 15, 'min_samples_split': 9, 'min_samples_leaf': 4, 'max_features': None, 'class_weight': None, 'random_state': 42}</t>
+  </si>
+  <si>
+    <t>DTC T/F</t>
+  </si>
+  <si>
+    <t>0: 0.72
+1: 0.79</t>
+  </si>
+  <si>
+    <t>0: 0.77
+1: 0.74</t>
+  </si>
+  <si>
+    <t>0: 0.74
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[307 91]
+ [121 349]]</t>
+  </si>
+  <si>
+    <t>DTC J/P</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.59
+1: 0.69</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.71</t>
+  </si>
+  <si>
+    <t>[[202 142]
+ [161 363]]</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.69
+1: 0.75</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.82</t>
+  </si>
+  <si>
+    <t>[[139 61]
+ [165 503]]</t>
+  </si>
+  <si>
+    <t>0: 0.59
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[71 49]
+ [126 622]]</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.87</t>
+  </si>
+  <si>
+    <t>[[116 84]
+ [90 578]]</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.51
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[64 56]
+ [69 679]]</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.74
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[149 51]
+ [184 484]]</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.93</t>
+  </si>
+  <si>
+    <t>[[54 66]
+ [47 701]]</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.76
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[151 49]
+ [184 484]]</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[62 58]
+ [67 681]]</t>
+  </si>
+  <si>
+    <t>[[145 55]
+ [263 405]]</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.63
+1: 0.71</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[76 44]
+ [220 528]]</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.75</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[120 80]
+ [164 504]]</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.85</t>
+  </si>
+  <si>
+    <t>[[64 56]
+ [150 598]]</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.70
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.54
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[140 60]
+ [179 489]]</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.63
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.86</t>
+  </si>
+  <si>
+    <t>[[76 44]
+ [149 599]]</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.61
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.86</t>
+  </si>
+  <si>
+    <t>[[122 78]
+ [101 567]]</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.91</t>
+  </si>
+  <si>
+    <t>[[64 56]
+ [70 678]]</t>
+  </si>
+  <si>
+    <t>0: 0.72
+1: 0.74</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[144 56]
+ [175 493]]</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[54 66]
+ [60 688]]</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.86</t>
+  </si>
+  <si>
+    <t>[[113 87]
+ [99 569]]</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[47 73]
+ [55 693]]</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.58</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.70</t>
+  </si>
+  <si>
+    <t>[[146 54]
+ [280 388]]</t>
+  </si>
+  <si>
+    <t>0: 0.22
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.62</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.74</t>
+  </si>
+  <si>
+    <t>[[82 38]
+ [284 464]]</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.70</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[124 76]
+ [201 467]]</t>
+  </si>
+  <si>
+    <t>0: 0.29
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.75</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[75 45]
+ [188 560]]</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.70</t>
+  </si>
+  <si>
+    <t>0: 0.54
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[146 54]
+ [199 469]]</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.95</t>
+  </si>
+  <si>
+    <t>0: 0.72
+1: 0.77</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.85</t>
+  </si>
+  <si>
+    <t>[[87 33]
+ [170 578]]</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[136 64]
+ [134 534]]</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.90</t>
+  </si>
+  <si>
+    <t>[[69 51]
+ [77 671]]</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.89</t>
+  </si>
+  <si>
+    <t>[[81 39]
+ [113 635]]</t>
+  </si>
+  <si>
+    <t>0: 0.66
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[132 68]
+ [134 534]]</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[69 51]
+ [69 679]]</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.65
+1: 0.75</t>
+  </si>
+  <si>
+    <t>[[130 70]
+ [165 503]]</t>
+  </si>
+  <si>
+    <t>0: 0.33
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.82</t>
+  </si>
+  <si>
+    <t>[[64 56]
+ [131 617]]</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.65
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.51
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[130 70]
+ [179 489]]</t>
+  </si>
+  <si>
+    <t>0: 0.51
+1: 0.90</t>
+  </si>
+  <si>
+    <t>[[76 44]
+ [104 644]]</t>
   </si>
   <si>
     <t>0: 0.41
@@ -68,17 +1000,10 @@
 1: 0.77</t>
   </si>
   <si>
-    <t>0: 200
-1: 668</t>
-  </si>
-  <si>
     <t>[[150 50]
  [220 448]]</t>
   </si>
   <si>
-    <t>LR S/N</t>
-  </si>
-  <si>
     <t>0: 0.33
 1: 0.95</t>
   </si>
@@ -91,66 +1016,10 @@
 1: 0.84</t>
   </si>
   <si>
-    <t>0: 120
-1: 748</t>
-  </si>
-  <si>
     <t>[[88 32]
  [181 567]]</t>
   </si>
   <si>
-    <t>LR T/F</t>
-  </si>
-  <si>
-    <t>0: 0.77
-1: 0.81</t>
-  </si>
-  <si>
-    <t>0: 0.78
-1: 0.80</t>
-  </si>
-  <si>
-    <t>0: 0.78
-1: 0.81</t>
-  </si>
-  <si>
-    <t>0: 398
-1: 470</t>
-  </si>
-  <si>
-    <t>[[312 86]
- [95 375]]</t>
-  </si>
-  <si>
-    <t>LR J/P</t>
-  </si>
-  <si>
-    <t>0: 0.66
-1: 0.82</t>
-  </si>
-  <si>
-    <t>0: 0.75
-1: 0.74</t>
-  </si>
-  <si>
-    <t>0: 0.70
-1: 0.78</t>
-  </si>
-  <si>
-    <t>0: 344
-1: 524</t>
-  </si>
-  <si>
-    <t>[[257 87]
- [134 390]]</t>
-  </si>
-  <si>
-    <t>{'n_estimators': 352, 'max_depth': 8, 'learning_rate': 0.041694500859353036, 'subsample': 0.6688508428769014, 'colsample_bytree': 0.6246885857257476, 'gamma': 0.6844100651211652, 'tree_method': 'hist', 'device': 'cuda', 'random_state': 42, 'n_jobs': 1}</t>
-  </si>
-  <si>
-    <t>XGB E/I</t>
-  </si>
-  <si>
     <t>0: 0.47
 1: 0.90</t>
   </si>
@@ -167,9 +1036,6 @@
  [161 507]]</t>
   </si>
   <si>
-    <t>XGB S/N</t>
-  </si>
-  <si>
     <t>0: 0.43
 1: 0.93</t>
   </si>
@@ -186,65 +1052,14 @@
  [98 650]]</t>
   </si>
   <si>
-    <t>XGB T/F</t>
-  </si>
-  <si>
-    <t>0: 0.80
-1: 0.84</t>
-  </si>
-  <si>
-    <t>0: 0.81
-1: 0.83</t>
-  </si>
-  <si>
-    <t>[[324 74]
- [82 388]]</t>
-  </si>
-  <si>
-    <t>XGB J/P</t>
-  </si>
-  <si>
-    <t>0: 0.75
-1: 0.78</t>
-  </si>
-  <si>
-    <t>0: 0.63
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.69
-1: 0.82</t>
-  </si>
-  <si>
-    <t>[[217 127]
- [72 452]]</t>
-  </si>
-  <si>
-    <t>{'loss': 'squared_hinge', 'C': 9.605448156429867, 'tol': 0.0004119653918147926, 'fit_intercept': False, 'random_state': 42, 'class_weight': 'balanced', 'max_iter': 5000}</t>
-  </si>
-  <si>
-    <t>LSVC E/I</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.91</t>
-  </si>
-  <si>
     <t>0: 0.77
 1: 0.73</t>
   </si>
   <si>
-    <t>0: 0.57
-1: 0.81</t>
-  </si>
-  <si>
     <t>[[153 47]
  [180 488]]</t>
   </si>
   <si>
-    <t>LSVC S/N</t>
-  </si>
-  <si>
     <t>0: 0.47
 1: 0.94</t>
   </si>
@@ -261,50 +1076,6 @@
  [84 664]]</t>
   </si>
   <si>
-    <t>LSVC T/F</t>
-  </si>
-  <si>
-    <t>0: 0.75
-1: 0.82</t>
-  </si>
-  <si>
-    <t>0: 0.80
-1: 0.78</t>
-  </si>
-  <si>
-    <t>0: 0.77
-1: 0.80</t>
-  </si>
-  <si>
-    <t>[[318 80]
- [105 365]]</t>
-  </si>
-  <si>
-    <t>LSVC J/P</t>
-  </si>
-  <si>
-    <t>0: 0.69
-1: 0.79</t>
-  </si>
-  <si>
-    <t>0: 0.68
-1: 0.80</t>
-  </si>
-  <si>
-    <t>0: 0.68
-1: 0.79</t>
-  </si>
-  <si>
-    <t>[[234 110]
- [107 417]]</t>
-  </si>
-  <si>
-    <t>{'hidden_layer_sizes': (256, 128, 64), 'activation': 'tanh', 'solver': 'adam', 'learning_rate': 'constant', 'learning_rate_init': 0.001, 'early_stopping': True, 'max_iter': 6000, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>MLPC E/I</t>
-  </si>
-  <si>
     <t>0: 0.73
 1: 0.75</t>
   </si>
@@ -313,17 +1084,6 @@
  [167 501]]</t>
   </si>
   <si>
-    <t>MLPC S/N</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.94</t>
-  </si>
-  <si>
-    <t>0: 0.68
-1: 0.85</t>
-  </si>
-  <si>
     <t>0: 0.52
 1: 0.90</t>
   </si>
@@ -332,42 +1092,6 @@
  [111 637]]</t>
   </si>
   <si>
-    <t>MLPC T/F</t>
-  </si>
-  <si>
-    <t>0: 0.79
-1: 0.82</t>
-  </si>
-  <si>
-    <t>0: 0.79
-1: 0.83</t>
-  </si>
-  <si>
-    <t>[[314 84]
- [82 388]]</t>
-  </si>
-  <si>
-    <t>MLPC J/P</t>
-  </si>
-  <si>
-    <t>0: 0.62
-1: 0.90</t>
-  </si>
-  <si>
-    <t>0: 0.70
-1: 0.84</t>
-  </si>
-  <si>
-    <t>[[212 132]
- [52 472]]</t>
-  </si>
-  <si>
-    <t>{'n_neighbors': 2, 'weights': 'distance', 'algorithm': 'brute', 'leaf_size': 14, 'metric': 'cosine', 'n_jobs': -1}</t>
-  </si>
-  <si>
-    <t>KNC E/I</t>
-  </si>
-  <si>
     <t>0: 0.42
 1: 0.88</t>
   </si>
@@ -384,13 +1108,6 @@
  [188 480]]</t>
   </si>
   <si>
-    <t>KNC S/N</t>
-  </si>
-  <si>
-    <t>0: 0.34
-1: 0.93</t>
-  </si>
-  <si>
     <t>0: 0.60
 1: 0.81</t>
   </si>
@@ -403,42 +1120,6 @@
  [141 607]]</t>
   </si>
   <si>
-    <t>KNC T/F</t>
-  </si>
-  <si>
-    <t>0: 0.73
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[290 108]
- [108 362]]</t>
-  </si>
-  <si>
-    <t>KNC J/P</t>
-  </si>
-  <si>
-    <t>0: 0.55
-1: 0.70</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.71</t>
-  </si>
-  <si>
-    <t>0: 0.54
-1: 0.71</t>
-  </si>
-  <si>
-    <t>[[184 160]
- [150 374]]</t>
-  </si>
-  <si>
-    <t>{'criterion': 'gini', 'max_depth': 15, 'min_samples_split': 9, 'min_samples_leaf': 4, 'max_features': None, 'class_weight': None, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>DTC E/I</t>
-  </si>
-  <si>
     <t>0: 0.42
 1: 0.89</t>
   </si>
@@ -451,9 +1132,6 @@
  [194 474]]</t>
   </si>
   <si>
-    <t>DTC S/N</t>
-  </si>
-  <si>
     <t>0: 0.39
 1: 0.94</t>
   </si>
@@ -462,686 +1140,8 @@
 1: 0.83</t>
   </si>
   <si>
-    <t>0: 0.49
-1: 0.88</t>
-  </si>
-  <si>
     <t>[[80 40]
  [126 622]]</t>
-  </si>
-  <si>
-    <t>DTC T/F</t>
-  </si>
-  <si>
-    <t>0: 0.72
-1: 0.79</t>
-  </si>
-  <si>
-    <t>0: 0.77
-1: 0.74</t>
-  </si>
-  <si>
-    <t>0: 0.74
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[307 91]
- [121 349]]</t>
-  </si>
-  <si>
-    <t>DTC J/P</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.72</t>
-  </si>
-  <si>
-    <t>0: 0.59
-1: 0.69</t>
-  </si>
-  <si>
-    <t>0: 0.57
-1: 0.71</t>
-  </si>
-  <si>
-    <t>[[202 142]
- [161 363]]</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.66
-1: 0.75</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.81</t>
-  </si>
-  <si>
-    <t>[[132 68]
- [164 504]]</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.61
-1: 0.82</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.87</t>
-  </si>
-  <si>
-    <t>[[73 47]
- [132 616]]</t>
-  </si>
-  <si>
-    <t>0: 0.57
-1: 0.87</t>
-  </si>
-  <si>
-    <t>[[115 85]
- [88 580]]</t>
-  </si>
-  <si>
-    <t>0: 0.48
-1: 0.92</t>
-  </si>
-  <si>
-    <t>[[58 62]
- [63 685]]</t>
-  </si>
-  <si>
-    <t>0: 0.74
-1: 0.73</t>
-  </si>
-  <si>
-    <t>[[149 51]
- [178 490]]</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.48
-1: 0.89</t>
-  </si>
-  <si>
-    <t>[[72 48]
- [108 640]]</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.64
-1: 0.85</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.87</t>
-  </si>
-  <si>
-    <t>[[128 72]
- [101 567]]</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 0.44
-1: 0.90</t>
-  </si>
-  <si>
-    <t>[[59 61]
- [92 656]]</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.72
-1: 0.61</t>
-  </si>
-  <si>
-    <t>0: 0.48
-1: 0.72</t>
-  </si>
-  <si>
-    <t>[[144 56]
- [258 410]]</t>
-  </si>
-  <si>
-    <t>0: 0.24
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.68
-1: 0.66</t>
-  </si>
-  <si>
-    <t>0: 0.35
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[81 39]
- [257 491]]</t>
-  </si>
-  <si>
-    <t>0: 0.41
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.63
-1: 0.73</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.79</t>
-  </si>
-  <si>
-    <t>[[126 74]
- [182 486]]</t>
-  </si>
-  <si>
-    <t>0: 0.30
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.59
-1: 0.78</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.84</t>
-  </si>
-  <si>
-    <t>[[71 49]
- [165 583]]</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.69
-1: 0.75</t>
-  </si>
-  <si>
-    <t>0: 0.55
-1: 0.82</t>
-  </si>
-  <si>
-    <t>[[139 61]
- [165 503]]</t>
-  </si>
-  <si>
-    <t>0: 0.59
-1: 0.83</t>
-  </si>
-  <si>
-    <t>[[71 49]
- [126 622]]</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.58
-1: 0.87</t>
-  </si>
-  <si>
-    <t>[[116 84]
- [90 578]]</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 0.51
-1: 0.92</t>
-  </si>
-  <si>
-    <t>[[64 56]
- [69 679]]</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.90</t>
-  </si>
-  <si>
-    <t>0: 0.74
-1: 0.72</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.80</t>
-  </si>
-  <si>
-    <t>[[149 51]
- [184 484]]</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.94</t>
-  </si>
-  <si>
-    <t>0: 0.49
-1: 0.93</t>
-  </si>
-  <si>
-    <t>[[54 66]
- [47 701]]</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 0.76
-1: 0.72</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.81</t>
-  </si>
-  <si>
-    <t>[[151 49]
- [184 484]]</t>
-  </si>
-  <si>
-    <t>0: 0.52
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.92</t>
-  </si>
-  <si>
-    <t>[[62 58]
- [67 681]]</t>
-  </si>
-  <si>
-    <t>[[145 55]
- [263 405]]</t>
-  </si>
-  <si>
-    <t>0: 0.26
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.63
-1: 0.71</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.80</t>
-  </si>
-  <si>
-    <t>[[76 44]
- [220 528]]</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.75</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.81</t>
-  </si>
-  <si>
-    <t>[[120 80]
- [164 504]]</t>
-  </si>
-  <si>
-    <t>0: 0.30
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.80</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.85</t>
-  </si>
-  <si>
-    <t>[[64 56]
- [150 598]]</t>
-  </si>
-  <si>
-    <t>0: 0.44
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.70
-1: 0.73</t>
-  </si>
-  <si>
-    <t>0: 0.54
-1: 0.80</t>
-  </si>
-  <si>
-    <t>[[140 60]
- [179 489]]</t>
-  </si>
-  <si>
-    <t>0: 0.63
-1: 0.80</t>
-  </si>
-  <si>
-    <t>0: 0.44
-1: 0.86</t>
-  </si>
-  <si>
-    <t>[[76 44]
- [149 599]]</t>
-  </si>
-  <si>
-    <t>0: 0.55
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.61
-1: 0.85</t>
-  </si>
-  <si>
-    <t>0: 0.58
-1: 0.86</t>
-  </si>
-  <si>
-    <t>[[122 78]
- [101 567]]</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.91</t>
-  </si>
-  <si>
-    <t>[[64 56]
- [70 678]]</t>
-  </si>
-  <si>
-    <t>0: 0.72
-1: 0.74</t>
-  </si>
-  <si>
-    <t>0: 0.55
-1: 0.81</t>
-  </si>
-  <si>
-    <t>[[144 56]
- [175 493]]</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.92</t>
-  </si>
-  <si>
-    <t>[[54 66]
- [60 688]]</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.85</t>
-  </si>
-  <si>
-    <t>0: 0.55
-1: 0.86</t>
-  </si>
-  <si>
-    <t>[[113 87]
- [99 569]]</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.90</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.92</t>
-  </si>
-  <si>
-    <t>[[47 73]
- [55 693]]</t>
-  </si>
-  <si>
-    <t>0: 0.34
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.73
-1: 0.58</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.70</t>
-  </si>
-  <si>
-    <t>[[146 54]
- [280 388]]</t>
-  </si>
-  <si>
-    <t>0: 0.22
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.68
-1: 0.62</t>
-  </si>
-  <si>
-    <t>0: 0.34
-1: 0.74</t>
-  </si>
-  <si>
-    <t>[[82 38]
- [284 464]]</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.62
-1: 0.70</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[124 76]
- [201 467]]</t>
-  </si>
-  <si>
-    <t>0: 0.29
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.62
-1: 0.75</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.83</t>
-  </si>
-  <si>
-    <t>[[75 45]
- [188 560]]</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.90</t>
-  </si>
-  <si>
-    <t>0: 0.73
-1: 0.70</t>
-  </si>
-  <si>
-    <t>0: 0.54
-1: 0.79</t>
-  </si>
-  <si>
-    <t>[[146 54]
- [199 469]]</t>
-  </si>
-  <si>
-    <t>0: 0.34
-1: 0.95</t>
-  </si>
-  <si>
-    <t>0: 0.72
-1: 0.77</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.85</t>
-  </si>
-  <si>
-    <t>[[87 33]
- [170 578]]</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.58
-1: 0.84</t>
-  </si>
-  <si>
-    <t>[[136 64]
- [134 534]]</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.57
-1: 0.90</t>
-  </si>
-  <si>
-    <t>[[69 51]
- [77 671]]</t>
-  </si>
-  <si>
-    <t>0: 0.52
-1: 0.89</t>
-  </si>
-  <si>
-    <t>[[81 39]
- [113 635]]</t>
-  </si>
-  <si>
-    <t>0: 0.66
-1: 0.80</t>
-  </si>
-  <si>
-    <t>0: 0.57
-1: 0.84</t>
-  </si>
-  <si>
-    <t>[[132 68]
- [134 534]]</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.57
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.92</t>
-  </si>
-  <si>
-    <t>[[69 51]
- [69 679]]</t>
-  </si>
-  <si>
-    <t>0: 0.44
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.65
-1: 0.75</t>
-  </si>
-  <si>
-    <t>[[130 70]
- [165 503]]</t>
-  </si>
-  <si>
-    <t>0: 0.33
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.82</t>
-  </si>
-  <si>
-    <t>[[64 56]
- [131 617]]</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.65
-1: 0.73</t>
-  </si>
-  <si>
-    <t>0: 0.51
-1: 0.80</t>
-  </si>
-  <si>
-    <t>[[130 70]
- [179 489]]</t>
-  </si>
-  <si>
-    <t>0: 0.51
-1: 0.90</t>
-  </si>
-  <si>
-    <t>[[76 44]
- [104 644]]</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1169,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1209,6 +1209,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFC404"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1255,7 +1261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1303,6 +1309,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1639,65 +1651,65 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="4">
         <v>0.73</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="D5" s="4" t="s">
-        <v>136</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" s="4">
         <v>0.79</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
@@ -1724,7 +1736,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
@@ -1764,103 +1776,103 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="C9" s="8" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F9" s="8">
         <v>0.8</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="8">
+    <row r="10" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="18">
         <v>0.86</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>141</v>
+      <c r="G10" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="7" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="18">
         <v>0.82</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>47</v>
+      <c r="G11" s="17" t="s">
+        <v>43</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>31</v>
@@ -1869,7 +1881,7 @@
         <v>0.77</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -1889,76 +1901,76 @@
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F14" s="10">
         <v>0.74</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F15" s="10">
         <v>0.82</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="9" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>25</v>
@@ -1967,25 +1979,25 @@
         <v>0.79</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>31</v>
@@ -1994,7 +2006,7 @@
         <v>0.75</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -2014,76 +2026,76 @@
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="12">
+    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="18">
         <v>0.8</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>151</v>
+      <c r="G19" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>153</v>
-      </c>
       <c r="E20" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F20" s="12">
         <v>0.82</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="11" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="D21" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>25</v>
@@ -2092,34 +2104,34 @@
         <v>0.81</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="12" t="s">
+      <c r="E22" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="18">
+        <v>0.79</v>
+      </c>
+      <c r="G22" s="17" t="s">
         <v>88</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -2139,76 +2151,76 @@
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>157</v>
-      </c>
       <c r="E24" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F24" s="14">
         <v>0.64</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>161</v>
-      </c>
       <c r="E25" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F25" s="14">
         <v>0.66</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="13" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>25</v>
@@ -2217,25 +2229,25 @@
         <v>0.75</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="D27" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>108</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>31</v>
@@ -2244,7 +2256,7 @@
         <v>0.64</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -2264,76 +2276,76 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>165</v>
-      </c>
       <c r="E29" s="16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F29" s="16">
         <v>0.71</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>168</v>
-      </c>
       <c r="D30" s="16" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F30" s="16">
         <v>0.75</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="15" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="C31" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>122</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>123</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>25</v>
@@ -2342,25 +2354,25 @@
         <v>0.76</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="C32" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="D32" s="16" t="s">
         <v>127</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>128</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>31</v>
@@ -2369,7 +2381,7 @@
         <v>0.65</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -2415,65 +2427,65 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="4">
         <v>0.74</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>130</v>
+        <v>8</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" s="4">
         <v>0.8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
@@ -2500,7 +2512,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
@@ -2540,76 +2552,76 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F9" s="8">
         <v>0.8</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F10" s="8">
         <v>0.86</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="7" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>25</v>
@@ -2618,25 +2630,25 @@
         <v>0.82</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>31</v>
@@ -2645,7 +2657,7 @@
         <v>0.77</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -2665,76 +2677,76 @@
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F14" s="10">
         <v>0.73</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>186</v>
+        <v>144</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F15" s="10">
         <v>0.87</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="9" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>25</v>
@@ -2743,25 +2755,25 @@
         <v>0.79</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>31</v>
@@ -2770,7 +2782,7 @@
         <v>0.75</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -2790,76 +2802,76 @@
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F19" s="12">
         <v>0.73</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F20" s="12">
         <v>0.86</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="11" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="D21" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>25</v>
@@ -2868,25 +2880,25 @@
         <v>0.81</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>87</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>89</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>31</v>
@@ -2895,7 +2907,7 @@
         <v>0.79</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -2915,76 +2927,76 @@
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>157</v>
-      </c>
       <c r="E24" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F24" s="14">
         <v>0.63</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>197</v>
+        <v>155</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F25" s="14">
         <v>0.7</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="13" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>25</v>
@@ -2993,25 +3005,25 @@
         <v>0.75</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="D27" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>108</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>31</v>
@@ -3020,7 +3032,7 @@
         <v>0.64</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -3040,76 +3052,76 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F29" s="16">
         <v>0.72</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F30" s="16">
         <v>0.76</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="15" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="C31" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>122</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>123</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>25</v>
@@ -3118,25 +3130,25 @@
         <v>0.76</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="C32" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="D32" s="16" t="s">
         <v>127</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>128</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>31</v>
@@ -3145,7 +3157,7 @@
         <v>0.65</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -3190,65 +3202,65 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>212</v>
+        <v>170</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" s="4">
         <v>0.72</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F4" s="4">
         <v>0.78</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -3275,7 +3287,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
@@ -3315,76 +3327,76 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" s="8">
         <v>0.79</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>221</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F9" s="8">
         <v>0.85</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>222</v>
+        <v>181</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="7" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>25</v>
@@ -3393,25 +3405,25 @@
         <v>0.82</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>31</v>
@@ -3420,7 +3432,7 @@
         <v>0.77</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -3440,76 +3452,76 @@
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>224</v>
-      </c>
       <c r="E13" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F13" s="10">
         <v>0.73</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F14" s="10">
         <v>0.85</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="9" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>25</v>
@@ -3518,25 +3530,25 @@
         <v>0.79</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>31</v>
@@ -3545,7 +3557,7 @@
         <v>0.75</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -3565,76 +3577,76 @@
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>231</v>
+        <v>190</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>232</v>
+        <v>191</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F18" s="12">
         <v>0.79</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F19" s="12">
         <v>0.85</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="11" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="D20" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>25</v>
@@ -3643,25 +3655,25 @@
         <v>0.81</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>87</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>89</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>31</v>
@@ -3670,7 +3682,7 @@
         <v>0.79</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -3690,76 +3702,76 @@
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>239</v>
+        <v>198</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>240</v>
+        <v>199</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F23" s="14">
         <v>0.62</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>242</v>
+        <v>201</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>243</v>
+        <v>202</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>244</v>
+        <v>203</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F24" s="14">
         <v>0.63</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="13" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>25</v>
@@ -3768,25 +3780,25 @@
         <v>0.75</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="D26" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>108</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>31</v>
@@ -3795,7 +3807,7 @@
         <v>0.64</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -3815,76 +3827,76 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F28" s="16">
         <v>0.68</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F29" s="16">
         <v>0.73</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="15" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="C30" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="D30" s="16" t="s">
         <v>122</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>123</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>25</v>
@@ -3893,25 +3905,25 @@
         <v>0.76</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="C31" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>127</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>128</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>31</v>
@@ -3920,7 +3932,7 @@
         <v>0.65</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -3966,65 +3978,65 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>255</v>
+        <v>214</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" s="4">
         <v>0.71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>258</v>
+        <v>217</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F4" s="4">
         <v>0.77</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -4051,7 +4063,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
@@ -4091,76 +4103,76 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>263</v>
+        <v>222</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" s="8">
         <v>0.77</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F9" s="8">
         <v>0.85</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>267</v>
+        <v>226</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="7" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>25</v>
@@ -4169,25 +4181,25 @@
         <v>0.82</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>31</v>
@@ -4196,7 +4208,7 @@
         <v>0.77</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -4216,76 +4228,76 @@
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F13" s="10">
         <v>0.73</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F14" s="10">
         <v>0.82</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="9" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>25</v>
@@ -4294,25 +4306,25 @@
         <v>0.79</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>31</v>
@@ -4321,7 +4333,7 @@
         <v>0.75</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -4341,76 +4353,76 @@
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>270</v>
+        <v>231</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F18" s="12">
         <v>0.77</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F19" s="12">
         <v>0.86</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="11" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="D20" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>25</v>
@@ -4419,25 +4431,25 @@
         <v>0.81</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>87</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>89</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>31</v>
@@ -4446,7 +4458,7 @@
         <v>0.79</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -4466,76 +4478,76 @@
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F23" s="14">
         <v>0.73</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F24" s="14">
         <v>0.78</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="13" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>25</v>
@@ -4544,25 +4556,25 @@
         <v>0.75</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="D26" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>108</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>31</v>
@@ -4571,7 +4583,7 @@
         <v>0.64</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -4591,76 +4603,76 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F28" s="16">
         <v>0.71</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F29" s="16">
         <v>0.83</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="15" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="C30" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="D30" s="16" t="s">
         <v>122</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>123</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>25</v>
@@ -4669,25 +4681,25 @@
         <v>0.76</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="C31" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>127</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>128</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>31</v>
@@ -4696,7 +4708,7 @@
         <v>0.65</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -4742,65 +4754,65 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="F3" s="4">
         <v>0.69</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>254</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="F4" s="4">
         <v>0.75</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -4827,7 +4839,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
@@ -4867,76 +4879,76 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>35</v>
+        <v>258</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>36</v>
+        <v>259</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" s="8">
         <v>0.75</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>38</v>
+        <v>261</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>40</v>
+        <v>262</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>41</v>
+        <v>263</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>42</v>
+        <v>264</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F9" s="8">
         <v>0.83</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>43</v>
+        <v>265</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="7" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>25</v>
@@ -4945,25 +4957,25 @@
         <v>0.82</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>31</v>
@@ -4972,7 +4984,7 @@
         <v>0.77</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -4992,76 +5004,76 @@
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>56</v>
+        <v>266</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F13" s="10">
         <v>0.74</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>58</v>
+        <v>267</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>60</v>
+        <v>268</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>61</v>
+        <v>269</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>62</v>
+        <v>270</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F14" s="10">
         <v>0.85</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>63</v>
+        <v>271</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="9" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>25</v>
@@ -5070,25 +5082,25 @@
         <v>0.79</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>31</v>
@@ -5097,7 +5109,7 @@
         <v>0.75</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -5117,76 +5129,76 @@
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>35</v>
+        <v>258</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>76</v>
+        <v>272</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F18" s="12">
         <v>0.75</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F19" s="12">
         <v>0.83</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="11" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="D20" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>25</v>
@@ -5195,25 +5207,25 @@
         <v>0.81</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>87</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>89</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>31</v>
@@ -5222,7 +5234,7 @@
         <v>0.79</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -5242,76 +5254,76 @@
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>93</v>
+        <v>276</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>94</v>
+        <v>277</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>95</v>
+        <v>278</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F23" s="14">
         <v>0.71</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>96</v>
+        <v>279</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>99</v>
+        <v>280</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>100</v>
+        <v>281</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F24" s="14">
         <v>0.78</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>101</v>
+        <v>282</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="13" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>25</v>
@@ -5320,25 +5332,25 @@
         <v>0.75</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="D26" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>108</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>31</v>
@@ -5347,7 +5359,7 @@
         <v>0.64</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -5367,76 +5379,76 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>112</v>
+        <v>283</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>113</v>
+        <v>284</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>95</v>
+        <v>278</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F28" s="16">
         <v>0.71</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>114</v>
+        <v>285</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>116</v>
+        <v>286</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F29" s="16">
         <v>0.81</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>119</v>
+        <v>288</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="15" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="C30" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="D30" s="16" t="s">
         <v>122</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>123</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>25</v>
@@ -5445,25 +5457,25 @@
         <v>0.76</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="C31" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>127</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>128</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>31</v>
@@ -5472,7 +5484,7 @@
         <v>0.65</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>

--- a/resultados/Resultados_Roberta-Base-FT.xlsx
+++ b/resultados/Resultados_Roberta-Base-FT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UMA\TFG\TFG-Sistema-Recomendacion-Personalidad\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D07CAAA-7E8D-4F00-A309-8986C5B71F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B3D159-4F32-4F6E-B30D-30C0D871F147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SMOTE" sheetId="1" r:id="rId1"/>
